--- a/output/Data and Chart Outputs/india_npp_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/india_npp_generation_daily.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Daily" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -144,13 +144,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -175,10 +175,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -203,10 +203,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EB6834"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -231,10 +231,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -259,10 +259,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EDA100"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -287,10 +287,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="E87BA4"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -323,8 +323,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -350,8 +350,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -368,7 +368,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -382,7 +382,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -391,7 +391,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -406,9 +406,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>

--- a/output/Data and Chart Outputs/india_npp_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/india_npp_generation_daily.xlsx
@@ -706,7 +706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -752,12 +752,27 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A day whose total is more than 1.5x the centred 9-day median is re-fetched once and, if still out of line, left blank (re-tried on each run). The report for 2 April has given April-to-date (two days) under 'today's actual' (2021, 2023). Blank this run: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>SOURCE</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>CEA (Central Electricity Authority) via the National Power Portal, daily generation report sub-report 2: https://npp.gov.in/public-reports/cea/daily/dgr/DD-MM-YYYY/dgr2-YYYY-MM-DD.xls</t>
         </is>
@@ -877,19 +892,19 @@
         <v>44287</v>
       </c>
       <c r="B5" t="n">
-        <v>103384.07</v>
+        <v>100108.06</v>
       </c>
       <c r="C5" t="n">
-        <v>3812.6</v>
+        <v>3696.6</v>
       </c>
       <c r="D5" t="n">
-        <v>17.46</v>
+        <v>17.1</v>
       </c>
       <c r="E5" t="n">
-        <v>3396.68</v>
+        <v>3292.51</v>
       </c>
       <c r="F5" t="n">
-        <v>8538.530000000001</v>
+        <v>8254.709999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1357,19 +1372,19 @@
         <v>45017</v>
       </c>
       <c r="B29" t="n">
-        <v>112205.35</v>
+        <v>108965.99</v>
       </c>
       <c r="C29" t="n">
-        <v>2455.19</v>
+        <v>2392.39</v>
       </c>
       <c r="D29" t="n">
-        <v>34.41</v>
+        <v>33.3</v>
       </c>
       <c r="E29" t="n">
-        <v>3602.25</v>
+        <v>3473.3</v>
       </c>
       <c r="F29" t="n">
-        <v>8879.9</v>
+        <v>8660.23</v>
       </c>
     </row>
     <row r="30">
@@ -4342,22 +4357,22 @@
         <v>44288</v>
       </c>
       <c r="B93" t="n">
-        <v>571730</v>
+        <v>287910</v>
       </c>
       <c r="C93" t="n">
-        <v>241420</v>
+        <v>125420</v>
       </c>
       <c r="D93" t="n">
-        <v>6602790</v>
+        <v>3326780</v>
       </c>
       <c r="E93" t="n">
-        <v>208210</v>
+        <v>104040</v>
       </c>
       <c r="F93" t="n">
-        <v>720</v>
+        <v>360</v>
       </c>
       <c r="G93" t="n">
-        <v>7624870</v>
+        <v>3844510</v>
       </c>
     </row>
     <row r="94">
@@ -21109,22 +21124,22 @@
         <v>45018</v>
       </c>
       <c r="B822" t="n">
-        <v>438290</v>
+        <v>218620</v>
       </c>
       <c r="C822" t="n">
-        <v>118570</v>
+        <v>55770</v>
       </c>
       <c r="D822" t="n">
-        <v>6391640</v>
+        <v>3152280</v>
       </c>
       <c r="E822" t="n">
-        <v>254310</v>
+        <v>125360</v>
       </c>
       <c r="F822" t="n">
-        <v>2220</v>
+        <v>1110</v>
       </c>
       <c r="G822" t="n">
-        <v>7205030</v>
+        <v>3553140</v>
       </c>
     </row>
     <row r="823">

--- a/output/Data and Chart Outputs/india_npp_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/india_npp_generation_daily.xlsx
@@ -155,7 +155,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>India conventional generation by type (CEA daily report; excludes wind/solar) (to Sep/26)</a:t>
+              <a:t>India conventional generation by type (CEA daily report; excludes wind/solar) (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -176,7 +176,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2A78D6"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -185,12 +185,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$70</f>
+              <f>'Chart'!$B$2:$B$71</f>
             </numRef>
           </val>
         </ser>
@@ -213,12 +213,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$70</f>
+              <f>'Chart'!$C$2:$C$71</f>
             </numRef>
           </val>
         </ser>
@@ -232,7 +232,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="1BAF7A"/>
+              <a:srgbClr val="6E4B2A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -241,12 +241,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$70</f>
+              <f>'Chart'!$D$2:$D$71</f>
             </numRef>
           </val>
         </ser>
@@ -260,7 +260,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EDA100"/>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -269,12 +269,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$70</f>
+              <f>'Chart'!$E$2:$E$71</f>
             </numRef>
           </val>
         </ser>
@@ -288,7 +288,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="2A78D6"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -297,12 +297,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$70</f>
+              <f>'Chart'!$F$2:$F$71</f>
             </numRef>
           </val>
         </ser>
@@ -744,7 +744,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Daily from 2021-01-01 to 2026-09-30. CONVENTIONAL generation only - wind, solar, biomass and small hydro are not in this report, and imports from Bhutan are excluded. India's full generation mix on the dashboard is Ember's (compiled from Grid-India) until a raw renewables feed is added.</t>
+          <t>Daily from 2021-01-01 to 2026-10-06. CONVENTIONAL generation only - wind, solar, biomass and small hydro are not in this report, and imports from Bhutan are excluded. India's full generation mix on the dashboard is Ember's (compiled from Grid-India) until a raw renewables feed is added.</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2205,6 +2205,26 @@
       </c>
       <c r="F70" t="n">
         <v>18670.09</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B71" t="n">
+        <v>23871.1</v>
+      </c>
+      <c r="C71" t="n">
+        <v>857.98</v>
+      </c>
+      <c r="D71" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1104.17</v>
+      </c>
+      <c r="F71" t="n">
+        <v>3164.21</v>
       </c>
     </row>
   </sheetData>
@@ -2219,7 +2239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2099"/>
+  <dimension ref="A1:G2105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50513,6 +50533,144 @@
         <v>4807520</v>
       </c>
     </row>
+    <row r="2100">
+      <c r="A2100" s="4" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B2100" t="n">
+        <v>552000</v>
+      </c>
+      <c r="C2100" t="n">
+        <v>145510</v>
+      </c>
+      <c r="D2100" t="n">
+        <v>3929360</v>
+      </c>
+      <c r="E2100" t="n">
+        <v>174740</v>
+      </c>
+      <c r="F2100" t="n">
+        <v>1130</v>
+      </c>
+      <c r="G2100" t="n">
+        <v>4802740</v>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B2101" t="n">
+        <v>506240</v>
+      </c>
+      <c r="C2101" t="n">
+        <v>115210</v>
+      </c>
+      <c r="D2101" t="n">
+        <v>3892730</v>
+      </c>
+      <c r="E2101" t="n">
+        <v>181250</v>
+      </c>
+      <c r="F2101" t="n">
+        <v>1130</v>
+      </c>
+      <c r="G2101" t="n">
+        <v>4696560</v>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" s="4" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B2102" t="n">
+        <v>530590</v>
+      </c>
+      <c r="C2102" t="n">
+        <v>130330</v>
+      </c>
+      <c r="D2102" t="n">
+        <v>3973840</v>
+      </c>
+      <c r="E2102" t="n">
+        <v>185530</v>
+      </c>
+      <c r="F2102" t="n">
+        <v>1120</v>
+      </c>
+      <c r="G2102" t="n">
+        <v>4821410</v>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B2103" t="n">
+        <v>508340</v>
+      </c>
+      <c r="C2103" t="n">
+        <v>134090</v>
+      </c>
+      <c r="D2103" t="n">
+        <v>3949860</v>
+      </c>
+      <c r="E2103" t="n">
+        <v>185830</v>
+      </c>
+      <c r="F2103" t="n">
+        <v>1120</v>
+      </c>
+      <c r="G2103" t="n">
+        <v>4779240</v>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B2104" t="n">
+        <v>537780</v>
+      </c>
+      <c r="C2104" t="n">
+        <v>156380</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>4064660</v>
+      </c>
+      <c r="E2104" t="n">
+        <v>185900</v>
+      </c>
+      <c r="F2104" t="n">
+        <v>1130</v>
+      </c>
+      <c r="G2104" t="n">
+        <v>4945850</v>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B2105" t="n">
+        <v>529260</v>
+      </c>
+      <c r="C2105" t="n">
+        <v>176460</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>4060650</v>
+      </c>
+      <c r="E2105" t="n">
+        <v>190920</v>
+      </c>
+      <c r="F2105" t="n">
+        <v>1130</v>
+      </c>
+      <c r="G2105" t="n">
+        <v>4958420</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/india_npp_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/india_npp_generation_daily.xlsx
@@ -155,6 +155,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>India conventional generation by type (CEA daily report; excludes wind/solar) (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -744,7 +745,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Daily from 2021-01-01 to 2026-10-06. CONVENTIONAL generation only - wind, solar, biomass and small hydro are not in this report, and imports from Bhutan are excluded. India's full generation mix on the dashboard is Ember's (compiled from Grid-India) until a raw renewables feed is added.</t>
+          <t>Daily from 2021-01-01 to 2026-10-26. CONVENTIONAL generation only - wind, solar, biomass and small hydro are not in this report, and imports from Bhutan are excluded. India's full generation mix on the dashboard is Ember's (compiled from Grid-India) until a raw renewables feed is added.</t>
         </is>
       </c>
     </row>
@@ -2212,19 +2213,19 @@
         <v>46296</v>
       </c>
       <c r="B71" t="n">
-        <v>23871.1</v>
+        <v>103545.37</v>
       </c>
       <c r="C71" t="n">
-        <v>857.98</v>
+        <v>2786.99</v>
       </c>
       <c r="D71" t="n">
-        <v>6.76</v>
+        <v>29.5</v>
       </c>
       <c r="E71" t="n">
-        <v>1104.17</v>
+        <v>4893.22</v>
       </c>
       <c r="F71" t="n">
-        <v>3164.21</v>
+        <v>11179.17</v>
       </c>
     </row>
   </sheetData>
@@ -2239,7 +2240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2105"/>
+  <dimension ref="A1:G2125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50671,6 +50672,466 @@
         <v>4958420</v>
       </c>
     </row>
+    <row r="2106">
+      <c r="A2106" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B2106" t="n">
+        <v>527890</v>
+      </c>
+      <c r="C2106" t="n">
+        <v>180650</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>4071630</v>
+      </c>
+      <c r="E2106" t="n">
+        <v>186390</v>
+      </c>
+      <c r="F2106" t="n">
+        <v>1130</v>
+      </c>
+      <c r="G2106" t="n">
+        <v>4967690</v>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B2107" t="n">
+        <v>502890</v>
+      </c>
+      <c r="C2107" t="n">
+        <v>175500</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>4042070</v>
+      </c>
+      <c r="E2107" t="n">
+        <v>180440</v>
+      </c>
+      <c r="F2107" t="n">
+        <v>1140</v>
+      </c>
+      <c r="G2107" t="n">
+        <v>4902040</v>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B2108" t="n">
+        <v>480960</v>
+      </c>
+      <c r="C2108" t="n">
+        <v>153370</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>4063600</v>
+      </c>
+      <c r="E2108" t="n">
+        <v>181320</v>
+      </c>
+      <c r="F2108" t="n">
+        <v>1140</v>
+      </c>
+      <c r="G2108" t="n">
+        <v>4880390</v>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B2109" t="n">
+        <v>468230</v>
+      </c>
+      <c r="C2109" t="n">
+        <v>146950</v>
+      </c>
+      <c r="D2109" t="n">
+        <v>3969000</v>
+      </c>
+      <c r="E2109" t="n">
+        <v>190560</v>
+      </c>
+      <c r="F2109" t="n">
+        <v>1140</v>
+      </c>
+      <c r="G2109" t="n">
+        <v>4775880</v>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B2110" t="n">
+        <v>419660</v>
+      </c>
+      <c r="C2110" t="n">
+        <v>101940</v>
+      </c>
+      <c r="D2110" t="n">
+        <v>3874080</v>
+      </c>
+      <c r="E2110" t="n">
+        <v>191180</v>
+      </c>
+      <c r="F2110" t="n">
+        <v>1130</v>
+      </c>
+      <c r="G2110" t="n">
+        <v>4587990</v>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B2111" t="n">
+        <v>444920</v>
+      </c>
+      <c r="C2111" t="n">
+        <v>110630</v>
+      </c>
+      <c r="D2111" t="n">
+        <v>3975550</v>
+      </c>
+      <c r="E2111" t="n">
+        <v>190980</v>
+      </c>
+      <c r="F2111" t="n">
+        <v>1130</v>
+      </c>
+      <c r="G2111" t="n">
+        <v>4723210</v>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B2112" t="n">
+        <v>452890</v>
+      </c>
+      <c r="C2112" t="n">
+        <v>138680</v>
+      </c>
+      <c r="D2112" t="n">
+        <v>4099960</v>
+      </c>
+      <c r="E2112" t="n">
+        <v>190940</v>
+      </c>
+      <c r="F2112" t="n">
+        <v>1130</v>
+      </c>
+      <c r="G2112" t="n">
+        <v>4883600</v>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B2113" t="n">
+        <v>479160</v>
+      </c>
+      <c r="C2113" t="n">
+        <v>149440</v>
+      </c>
+      <c r="D2113" t="n">
+        <v>4192560</v>
+      </c>
+      <c r="E2113" t="n">
+        <v>189930</v>
+      </c>
+      <c r="F2113" t="n">
+        <v>1130</v>
+      </c>
+      <c r="G2113" t="n">
+        <v>5012220</v>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B2114" t="n">
+        <v>466510</v>
+      </c>
+      <c r="C2114" t="n">
+        <v>143360</v>
+      </c>
+      <c r="D2114" t="n">
+        <v>4095420</v>
+      </c>
+      <c r="E2114" t="n">
+        <v>190450</v>
+      </c>
+      <c r="F2114" t="n">
+        <v>1140</v>
+      </c>
+      <c r="G2114" t="n">
+        <v>4896880</v>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B2115" t="n">
+        <v>436840</v>
+      </c>
+      <c r="C2115" t="n">
+        <v>113250</v>
+      </c>
+      <c r="D2115" t="n">
+        <v>4112860</v>
+      </c>
+      <c r="E2115" t="n">
+        <v>189910</v>
+      </c>
+      <c r="F2115" t="n">
+        <v>1140</v>
+      </c>
+      <c r="G2115" t="n">
+        <v>4854000</v>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B2116" t="n">
+        <v>403850</v>
+      </c>
+      <c r="C2116" t="n">
+        <v>90280</v>
+      </c>
+      <c r="D2116" t="n">
+        <v>4108310</v>
+      </c>
+      <c r="E2116" t="n">
+        <v>187470</v>
+      </c>
+      <c r="F2116" t="n">
+        <v>1140</v>
+      </c>
+      <c r="G2116" t="n">
+        <v>4791050</v>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B2117" t="n">
+        <v>356580</v>
+      </c>
+      <c r="C2117" t="n">
+        <v>48780</v>
+      </c>
+      <c r="D2117" t="n">
+        <v>3971320</v>
+      </c>
+      <c r="E2117" t="n">
+        <v>188970</v>
+      </c>
+      <c r="F2117" t="n">
+        <v>1130</v>
+      </c>
+      <c r="G2117" t="n">
+        <v>4566780</v>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B2118" t="n">
+        <v>345370</v>
+      </c>
+      <c r="C2118" t="n">
+        <v>46020</v>
+      </c>
+      <c r="D2118" t="n">
+        <v>3952100</v>
+      </c>
+      <c r="E2118" t="n">
+        <v>190660</v>
+      </c>
+      <c r="F2118" t="n">
+        <v>1140</v>
+      </c>
+      <c r="G2118" t="n">
+        <v>4535290</v>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B2119" t="n">
+        <v>324800</v>
+      </c>
+      <c r="C2119" t="n">
+        <v>44650</v>
+      </c>
+      <c r="D2119" t="n">
+        <v>3749710</v>
+      </c>
+      <c r="E2119" t="n">
+        <v>191200</v>
+      </c>
+      <c r="F2119" t="n">
+        <v>1140</v>
+      </c>
+      <c r="G2119" t="n">
+        <v>4311500</v>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B2120" t="n">
+        <v>334610</v>
+      </c>
+      <c r="C2120" t="n">
+        <v>49430</v>
+      </c>
+      <c r="D2120" t="n">
+        <v>3863710</v>
+      </c>
+      <c r="E2120" t="n">
+        <v>191240</v>
+      </c>
+      <c r="F2120" t="n">
+        <v>1160</v>
+      </c>
+      <c r="G2120" t="n">
+        <v>4440150</v>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B2121" t="n">
+        <v>337230</v>
+      </c>
+      <c r="C2121" t="n">
+        <v>52950</v>
+      </c>
+      <c r="D2121" t="n">
+        <v>3982510</v>
+      </c>
+      <c r="E2121" t="n">
+        <v>190720</v>
+      </c>
+      <c r="F2121" t="n">
+        <v>1160</v>
+      </c>
+      <c r="G2121" t="n">
+        <v>4564570</v>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B2122" t="n">
+        <v>325620</v>
+      </c>
+      <c r="C2122" t="n">
+        <v>48040</v>
+      </c>
+      <c r="D2122" t="n">
+        <v>4001880</v>
+      </c>
+      <c r="E2122" t="n">
+        <v>190340</v>
+      </c>
+      <c r="F2122" t="n">
+        <v>1140</v>
+      </c>
+      <c r="G2122" t="n">
+        <v>4567020</v>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B2123" t="n">
+        <v>317620</v>
+      </c>
+      <c r="C2123" t="n">
+        <v>47490</v>
+      </c>
+      <c r="D2123" t="n">
+        <v>3996970</v>
+      </c>
+      <c r="E2123" t="n">
+        <v>191290</v>
+      </c>
+      <c r="F2123" t="n">
+        <v>1140</v>
+      </c>
+      <c r="G2123" t="n">
+        <v>4554510</v>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B2124" t="n">
+        <v>292730</v>
+      </c>
+      <c r="C2124" t="n">
+        <v>42720</v>
+      </c>
+      <c r="D2124" t="n">
+        <v>3775520</v>
+      </c>
+      <c r="E2124" t="n">
+        <v>191960</v>
+      </c>
+      <c r="F2124" t="n">
+        <v>1120</v>
+      </c>
+      <c r="G2124" t="n">
+        <v>4304050</v>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B2125" t="n">
+        <v>296600</v>
+      </c>
+      <c r="C2125" t="n">
+        <v>44880</v>
+      </c>
+      <c r="D2125" t="n">
+        <v>3775510</v>
+      </c>
+      <c r="E2125" t="n">
+        <v>193100</v>
+      </c>
+      <c r="F2125" t="n">
+        <v>1120</v>
+      </c>
+      <c r="G2125" t="n">
+        <v>4311210</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
